--- a/CSV/Trail Ruins.xlsx
+++ b/CSV/Trail Ruins.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EAFBD5-E30F-0443-820F-01C3A6A99F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A39C418-5D90-2B4D-9856-BDAE400F181D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19460" yWindow="780" windowWidth="10000" windowHeight="19100" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
+    <workbookView xWindow="0" yWindow="9780" windowWidth="11480" windowHeight="9780" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,13 +41,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>nummer</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
     <t>Z</t>
+  </si>
+  <si>
+    <t>Trail Ruins</t>
   </si>
 </sst>
 </file>
@@ -426,30 +426,415 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5459</v>
+      </c>
+      <c r="C2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5027</v>
+      </c>
+      <c r="C3">
+        <v>-2451</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4942</v>
+      </c>
+      <c r="C4">
+        <v>-3214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4594</v>
+      </c>
+      <c r="C5">
+        <v>-3602</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>4526</v>
+      </c>
+      <c r="C6">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>4467</v>
+      </c>
+      <c r="C7">
+        <v>-829</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>4451</v>
+      </c>
+      <c r="C8">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>4366</v>
+      </c>
+      <c r="C9">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>4158</v>
+      </c>
+      <c r="C10">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>4157</v>
+      </c>
+      <c r="C11">
+        <v>-5667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>4066</v>
+      </c>
+      <c r="C12">
+        <v>-3042</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>4061</v>
+      </c>
+      <c r="C13">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>3986</v>
+      </c>
+      <c r="C14">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>3965</v>
+      </c>
+      <c r="C15">
+        <v>-227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>3870</v>
+      </c>
+      <c r="C16">
+        <v>-1618</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>3539</v>
+      </c>
+      <c r="C17">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>3506</v>
+      </c>
+      <c r="C18">
+        <v>-1358</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>3309</v>
+      </c>
+      <c r="C19">
+        <v>-5357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>3037</v>
+      </c>
+      <c r="C20">
+        <v>-3987</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>2206</v>
+      </c>
+      <c r="C21">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>1826</v>
+      </c>
+      <c r="C22">
+        <v>-4078</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>1218</v>
+      </c>
+      <c r="C23">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>563</v>
+      </c>
+      <c r="C24">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>-530</v>
+      </c>
+      <c r="C25">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>-882</v>
+      </c>
+      <c r="C26">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>-1277</v>
+      </c>
+      <c r="C27">
+        <v>-989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>-1902</v>
+      </c>
+      <c r="C28">
+        <v>-4334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>-2083</v>
+      </c>
+      <c r="C29">
+        <v>-813</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>-2173</v>
+      </c>
+      <c r="C30">
+        <v>-317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>-2674</v>
+      </c>
+      <c r="C31">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>-2675</v>
+      </c>
+      <c r="C32">
+        <v>5677</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>-3005</v>
+      </c>
+      <c r="C33">
+        <v>5683</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>-3779</v>
+      </c>
+      <c r="C34">
+        <v>-1283</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>-4322</v>
+      </c>
+      <c r="C35">
+        <v>-2018</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>-5741</v>
+      </c>
+      <c r="C36">
+        <v>1203</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
+  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C39">
+      <sortCondition descending="1" ref="B1:B39"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
